--- a/Rules.xlsx
+++ b/Rules.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t xml:space="preserve">Rule No </t>
   </si>
@@ -323,52 +323,109 @@
     <t>This policy is a sample document to test the automation protype build for NYL using python.</t>
   </si>
   <si>
-    <t>R6.1</t>
+    <t>R7.0</t>
   </si>
   <si>
     <t>Monthly Claim Cost</t>
   </si>
   <si>
-    <t>Total Claim Cost</t>
+    <t>Total Claim Cost:EE</t>
   </si>
   <si>
     <t>∑&lt;Monthly Claim Cost&gt;</t>
   </si>
   <si>
-    <t>R6.2</t>
+    <t>R7.1</t>
   </si>
   <si>
     <t>Monthly FullProfit Premium</t>
   </si>
   <si>
-    <t>Total FullProfit Premium</t>
+    <t>Total FullProfit Premium:EE</t>
   </si>
   <si>
     <t>∑&lt;Monthly FullProfit Premium&gt;</t>
   </si>
   <si>
-    <t>R6.3</t>
+    <t>R7.2</t>
   </si>
   <si>
     <t>Monthly ZeroProfit Premium</t>
   </si>
   <si>
-    <t>Total ZeroProfit Premium</t>
+    <t>Total ZeroProfit Premium:EE</t>
   </si>
   <si>
     <t>∑&lt;Monthly ZeroProfit Premium&gt;</t>
   </si>
   <si>
-    <t>R6.4</t>
+    <t>R7.3</t>
   </si>
   <si>
     <t>Monthly Base Claim Cost</t>
   </si>
   <si>
-    <t>Total Base Claim Cost</t>
+    <t>Total Base Claim Cost:EE</t>
   </si>
   <si>
     <t>∑&lt;Monthly Base Claim Cost&gt;/∑&lt;Monthly ZeroProfit Premium&gt;</t>
+  </si>
+  <si>
+    <t>R7.4</t>
+  </si>
+  <si>
+    <t>Total Claim Cost:SPS</t>
+  </si>
+  <si>
+    <t>R7.5</t>
+  </si>
+  <si>
+    <t>Total FullProfit Premium:SPS</t>
+  </si>
+  <si>
+    <t>R7.6</t>
+  </si>
+  <si>
+    <t>Total ZeroProfit Premium:SPS</t>
+  </si>
+  <si>
+    <t>R7.7</t>
+  </si>
+  <si>
+    <t>Total Base Claim Cost:SPS</t>
+  </si>
+  <si>
+    <t>R7.8</t>
+  </si>
+  <si>
+    <t>Total Claim Cost:CH</t>
+  </si>
+  <si>
+    <t>R7.9</t>
+  </si>
+  <si>
+    <t>Total FullProfit Premium:CH</t>
+  </si>
+  <si>
+    <t>R7.10</t>
+  </si>
+  <si>
+    <t>Total ZeroProfit Premium:CH</t>
+  </si>
+  <si>
+    <t>R7.11</t>
+  </si>
+  <si>
+    <t>Total Base Claim Cost:CH</t>
+  </si>
+  <si>
+    <t>R8.0</t>
+  </si>
+  <si>
+    <t>∑&lt;Monthly ZeroProfit Premium&gt;,&lt;Monthly Claim Cost&gt;,&lt;Monthly FullProfit Premium&gt;,&lt;Monthly Base Claim Cost&gt;</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
   </si>
 </sst>
 </file>
@@ -419,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -441,6 +498,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -765,7 +825,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -779,70 +839,187 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="22" ht="14.25" customHeight="1"/>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/Rules.xlsx
+++ b/Rules.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="67">
   <si>
     <t xml:space="preserve">Rule No </t>
   </si>
@@ -426,6 +426,15 @@
   </si>
   <si>
     <t>Total Cost</t>
+  </si>
+  <si>
+    <t>R8.1</t>
+  </si>
+  <si>
+    <t>(∑&lt;Monthly ZeroProfit Premium&gt;,&lt;Monthly Claim Cost&gt;,&lt;Monthly FullProfit Premium&gt;,&lt;Monthly Base Claim Cost&gt;) x 12</t>
+  </si>
+  <si>
+    <t>Annual Total Cost</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1029,20 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>
